--- a/CPU Design/L1IsSequences.xlsx
+++ b/CPU Design/L1IsSequences.xlsx
@@ -579,7 +579,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4644" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4645" uniqueCount="230">
   <si>
     <t>STEP</t>
   </si>
@@ -630,9 +630,6 @@
   </si>
   <si>
     <t>x</t>
-  </si>
-  <si>
-    <t>INC PC</t>
   </si>
   <si>
     <t>H</t>
@@ -1291,6 +1288,12 @@
   </si>
   <si>
     <t>Deleted READ and WRITE from "Key" tab (missed that when I removed READ and WRITE globally)</t>
+  </si>
+  <si>
+    <t>INC_PC</t>
+  </si>
+  <si>
+    <t>Changed "INC PC" to "INC_PC" to make it consistent with other docs</t>
   </si>
 </sst>
 </file>
@@ -1737,30 +1740,30 @@
   <sheetData>
     <row r="1" spans="1:38" ht="53.15">
       <c r="A1" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>6</v>
@@ -1769,17 +1772,17 @@
         <v>7</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="O1" s="2"/>
       <c r="P1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>1</v>
@@ -1791,7 +1794,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="V1" s="2" t="s">
         <v>4</v>
@@ -1800,7 +1803,7 @@
         <v>5</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Y1" s="2"/>
       <c r="Z1" s="2" t="s">
@@ -1813,23 +1816,23 @@
         <v>8</v>
       </c>
       <c r="AD1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AG1" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="AH1" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AI1" s="13"/>
       <c r="AJ1" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AK1" s="1" t="s">
         <v>13</v>
@@ -1876,12 +1879,12 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="1"/>
       <c r="AL2" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:38">
       <c r="A3" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
@@ -1972,7 +1975,7 @@
         <v>15</v>
       </c>
       <c r="AK3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AL3" t="s">
         <v>14</v>
@@ -1980,7 +1983,7 @@
     </row>
     <row r="4" spans="1:38">
       <c r="A4" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="1">
         <v>0</v>
@@ -1989,7 +1992,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>15</v>
@@ -2070,7 +2073,7 @@
         <v>15</v>
       </c>
       <c r="AK4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -2084,7 +2087,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>15</v>
@@ -2114,7 +2117,7 @@
         <v>15</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S5" s="5" t="s">
         <v>15</v>
@@ -2162,7 +2165,7 @@
         <v>15</v>
       </c>
       <c r="AK5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -2176,7 +2179,7 @@
         <v>15</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>15</v>
@@ -2206,7 +2209,7 @@
         <v>15</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S6" s="5" t="s">
         <v>15</v>
@@ -2254,7 +2257,7 @@
         <v>15</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -2343,18 +2346,18 @@
         <v>15</v>
       </c>
       <c r="AJ7" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AL7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:38">
       <c r="A9" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
@@ -2444,15 +2447,15 @@
         <v>15</v>
       </c>
       <c r="AK9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:38">
       <c r="A10" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
@@ -2461,7 +2464,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>15</v>
@@ -2542,7 +2545,7 @@
         <v>15</v>
       </c>
       <c r="AK10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2553,7 +2556,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>15</v>
@@ -2631,18 +2634,18 @@
         <v>15</v>
       </c>
       <c r="AJ11" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL11" t="s">
         <v>20</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:38">
       <c r="A13" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
@@ -2732,12 +2735,12 @@
         <v>15</v>
       </c>
       <c r="AK13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:38">
       <c r="A14" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B14" s="1">
         <v>2</v>
@@ -2767,7 +2770,7 @@
         <v>15</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N14" s="5" t="s">
         <v>15</v>
@@ -2791,7 +2794,7 @@
         <v>15</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W14" s="5" t="s">
         <v>15</v>
@@ -2800,19 +2803,19 @@
         <v>15</v>
       </c>
       <c r="Z14" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA14" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB14" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD14" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE14" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF14" s="5" t="s">
         <v>15</v>
@@ -2827,12 +2830,12 @@
         <v>15</v>
       </c>
       <c r="AK14" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:38">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
@@ -2862,7 +2865,7 @@
         <v>15</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N15" s="5" t="s">
         <v>15</v>
@@ -2886,7 +2889,7 @@
         <v>15</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W15" s="5" t="s">
         <v>15</v>
@@ -2895,19 +2898,19 @@
         <v>15</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA15" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB15" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD15" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE15" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF15" s="5" t="s">
         <v>15</v>
@@ -2922,12 +2925,12 @@
         <v>15</v>
       </c>
       <c r="AK15" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:38">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
@@ -2990,13 +2993,13 @@
         <v>15</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA16" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB16" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD16" s="5" t="s">
         <v>15</v>
@@ -3017,12 +3020,12 @@
         <v>15</v>
       </c>
       <c r="AK16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:38">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
@@ -3052,7 +3055,7 @@
         <v>15</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N17" s="5" t="s">
         <v>15</v>
@@ -3079,19 +3082,19 @@
         <v>15</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X17" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA17" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB17" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD17" s="5" t="s">
         <v>15</v>
@@ -3100,7 +3103,7 @@
         <v>15</v>
       </c>
       <c r="AF17" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG17" s="5" t="s">
         <v>15</v>
@@ -3112,12 +3115,12 @@
         <v>15</v>
       </c>
       <c r="AK17" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:38">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
@@ -3147,7 +3150,7 @@
         <v>15</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N18" s="5" t="s">
         <v>15</v>
@@ -3174,19 +3177,19 @@
         <v>15</v>
       </c>
       <c r="W18" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X18" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Z18" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA18" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB18" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD18" s="5" t="s">
         <v>15</v>
@@ -3195,7 +3198,7 @@
         <v>15</v>
       </c>
       <c r="AF18" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG18" s="5" t="s">
         <v>15</v>
@@ -3207,12 +3210,12 @@
         <v>15</v>
       </c>
       <c r="AK18" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:38">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
@@ -3275,13 +3278,13 @@
         <v>15</v>
       </c>
       <c r="Z19" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA19" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB19" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD19" s="5" t="s">
         <v>15</v>
@@ -3302,7 +3305,7 @@
         <v>15</v>
       </c>
       <c r="AK19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3337,7 +3340,7 @@
         <v>15</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P20" s="5" t="s">
         <v>15</v>
@@ -3355,7 +3358,7 @@
         <v>15</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V20" s="5" t="s">
         <v>15</v>
@@ -3367,19 +3370,19 @@
         <v>15</v>
       </c>
       <c r="Z20" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA20" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB20" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD20" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE20" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF20" s="5" t="s">
         <v>15</v>
@@ -3394,7 +3397,7 @@
         <v>15</v>
       </c>
       <c r="AK20" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3429,7 +3432,7 @@
         <v>15</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P21" s="5" t="s">
         <v>15</v>
@@ -3447,7 +3450,7 @@
         <v>15</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V21" s="5" t="s">
         <v>15</v>
@@ -3459,19 +3462,19 @@
         <v>15</v>
       </c>
       <c r="Z21" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA21" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB21" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD21" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE21" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF21" s="5" t="s">
         <v>15</v>
@@ -3486,7 +3489,7 @@
         <v>15</v>
       </c>
       <c r="AK21" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:38">
@@ -3497,7 +3500,7 @@
         <v>9</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>15</v>
@@ -3551,42 +3554,42 @@
         <v>15</v>
       </c>
       <c r="Z22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK22" t="s">
         <v>28</v>
       </c>
-      <c r="AA22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AJ22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK22" t="s">
-        <v>29</v>
-      </c>
       <c r="AL22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:38">
       <c r="A24" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B24" s="1">
         <v>3</v>
@@ -3676,12 +3679,12 @@
         <v>15</v>
       </c>
       <c r="AK24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:38">
       <c r="A25" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B25" s="1">
         <v>3</v>
@@ -3711,7 +3714,7 @@
         <v>15</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N25" s="5" t="s">
         <v>15</v>
@@ -3735,7 +3738,7 @@
         <v>15</v>
       </c>
       <c r="V25" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W25" s="5" t="s">
         <v>15</v>
@@ -3744,19 +3747,19 @@
         <v>15</v>
       </c>
       <c r="Z25" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA25" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB25" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD25" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE25" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF25" s="5" t="s">
         <v>15</v>
@@ -3771,12 +3774,12 @@
         <v>15</v>
       </c>
       <c r="AK25" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:38">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" s="1">
         <v>3</v>
@@ -3806,7 +3809,7 @@
         <v>15</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N26" s="5" t="s">
         <v>15</v>
@@ -3830,7 +3833,7 @@
         <v>15</v>
       </c>
       <c r="V26" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W26" s="5" t="s">
         <v>15</v>
@@ -3839,19 +3842,19 @@
         <v>15</v>
       </c>
       <c r="Z26" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA26" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB26" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD26" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE26" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF26" s="5" t="s">
         <v>15</v>
@@ -3866,7 +3869,7 @@
         <v>15</v>
       </c>
       <c r="AK26" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:38">
@@ -3931,13 +3934,13 @@
         <v>15</v>
       </c>
       <c r="Z27" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA27" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB27" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD27" s="5" t="s">
         <v>15</v>
@@ -3958,7 +3961,7 @@
         <v>15</v>
       </c>
       <c r="AK27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:38">
@@ -3993,7 +3996,7 @@
         <v>15</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P28" s="5" t="s">
         <v>15</v>
@@ -4011,7 +4014,7 @@
         <v>15</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V28" s="5" t="s">
         <v>15</v>
@@ -4023,19 +4026,19 @@
         <v>15</v>
       </c>
       <c r="Z28" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA28" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB28" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD28" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE28" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF28" s="5" t="s">
         <v>15</v>
@@ -4050,7 +4053,7 @@
         <v>15</v>
       </c>
       <c r="AK28" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:38">
@@ -4085,7 +4088,7 @@
         <v>15</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P29" s="5" t="s">
         <v>15</v>
@@ -4103,7 +4106,7 @@
         <v>15</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V29" s="5" t="s">
         <v>15</v>
@@ -4115,19 +4118,19 @@
         <v>15</v>
       </c>
       <c r="Z29" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA29" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB29" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD29" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE29" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF29" s="5" t="s">
         <v>15</v>
@@ -4142,7 +4145,7 @@
         <v>15</v>
       </c>
       <c r="AK29" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:38">
@@ -4153,7 +4156,7 @@
         <v>6</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>15</v>
@@ -4207,42 +4210,42 @@
         <v>15</v>
       </c>
       <c r="Z30" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA30" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB30" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ30" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK30" t="s">
         <v>28</v>
       </c>
-      <c r="AA30" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB30" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AJ30" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK30" t="s">
-        <v>29</v>
-      </c>
       <c r="AL30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:38">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="1">
         <v>4</v>
@@ -4332,7 +4335,7 @@
         <v>15</v>
       </c>
       <c r="AK32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:38">
@@ -4364,13 +4367,13 @@
         <v>15</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N33" s="5" t="s">
         <v>15</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q33" s="5" t="s">
         <v>15</v>
@@ -4412,7 +4415,7 @@
         <v>15</v>
       </c>
       <c r="AF33" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG33" s="5" t="s">
         <v>15</v>
@@ -4424,7 +4427,7 @@
         <v>15</v>
       </c>
       <c r="AK33" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:38">
@@ -4456,13 +4459,13 @@
         <v>15</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N34" s="5" t="s">
         <v>15</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q34" s="5" t="s">
         <v>15</v>
@@ -4504,7 +4507,7 @@
         <v>15</v>
       </c>
       <c r="AF34" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG34" s="5" t="s">
         <v>15</v>
@@ -4516,7 +4519,7 @@
         <v>15</v>
       </c>
       <c r="AK34" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:38">
@@ -4608,7 +4611,7 @@
         <v>15</v>
       </c>
       <c r="AK35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:38">
@@ -4625,7 +4628,7 @@
         <v>15</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>15</v>
@@ -4661,7 +4664,7 @@
         <v>15</v>
       </c>
       <c r="U36" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V36" s="5" t="s">
         <v>15</v>
@@ -4685,7 +4688,7 @@
         <v>15</v>
       </c>
       <c r="AE36" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF36" s="5" t="s">
         <v>15</v>
@@ -4700,7 +4703,7 @@
         <v>15</v>
       </c>
       <c r="AK36" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:38">
@@ -4717,7 +4720,7 @@
         <v>15</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>15</v>
@@ -4753,7 +4756,7 @@
         <v>15</v>
       </c>
       <c r="U37" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V37" s="5" t="s">
         <v>15</v>
@@ -4777,7 +4780,7 @@
         <v>15</v>
       </c>
       <c r="AE37" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF37" s="5" t="s">
         <v>15</v>
@@ -4792,7 +4795,7 @@
         <v>15</v>
       </c>
       <c r="AK37" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:38">
@@ -4803,7 +4806,7 @@
         <v>6</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>15</v>
@@ -4881,18 +4884,18 @@
         <v>15</v>
       </c>
       <c r="AJ38" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:38">
       <c r="A40" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B40" s="1">
         <v>5</v>
@@ -4982,7 +4985,7 @@
         <v>15</v>
       </c>
       <c r="AK40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:38">
@@ -4993,10 +4996,10 @@
         <v>1</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>15</v>
@@ -5035,7 +5038,7 @@
         <v>15</v>
       </c>
       <c r="U41" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V41" s="5" t="s">
         <v>15</v>
@@ -5056,7 +5059,7 @@
         <v>16</v>
       </c>
       <c r="AD41" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE41" s="5" t="s">
         <v>15</v>
@@ -5074,7 +5077,7 @@
         <v>15</v>
       </c>
       <c r="AK41" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:38">
@@ -5088,7 +5091,7 @@
         <v>15</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>15</v>
@@ -5127,7 +5130,7 @@
         <v>15</v>
       </c>
       <c r="U42" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V42" s="5" t="s">
         <v>15</v>
@@ -5148,7 +5151,7 @@
         <v>16</v>
       </c>
       <c r="AD42" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE42" s="5" t="s">
         <v>15</v>
@@ -5166,7 +5169,7 @@
         <v>15</v>
       </c>
       <c r="AK42" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:38">
@@ -5177,7 +5180,7 @@
         <v>3</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>15</v>
@@ -5255,18 +5258,18 @@
         <v>15</v>
       </c>
       <c r="AJ43" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:38">
       <c r="A45" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B45" s="1">
         <v>6</v>
@@ -5356,7 +5359,7 @@
         <v>15</v>
       </c>
       <c r="AK45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:38">
@@ -5388,7 +5391,7 @@
         <v>15</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N46" s="5" t="s">
         <v>15</v>
@@ -5412,7 +5415,7 @@
         <v>15</v>
       </c>
       <c r="V46" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W46" s="5" t="s">
         <v>15</v>
@@ -5421,19 +5424,19 @@
         <v>15</v>
       </c>
       <c r="Z46" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA46" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB46" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD46" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE46" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF46" s="5" t="s">
         <v>15</v>
@@ -5448,7 +5451,7 @@
         <v>15</v>
       </c>
       <c r="AK46" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:38">
@@ -5480,7 +5483,7 @@
         <v>15</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N47" s="5" t="s">
         <v>15</v>
@@ -5504,7 +5507,7 @@
         <v>15</v>
       </c>
       <c r="V47" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W47" s="5" t="s">
         <v>15</v>
@@ -5513,19 +5516,19 @@
         <v>15</v>
       </c>
       <c r="Z47" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA47" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB47" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD47" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE47" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF47" s="5" t="s">
         <v>15</v>
@@ -5540,7 +5543,7 @@
         <v>15</v>
       </c>
       <c r="AK47" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:38">
@@ -5605,13 +5608,13 @@
         <v>15</v>
       </c>
       <c r="Z48" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA48" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB48" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD48" s="5" t="s">
         <v>15</v>
@@ -5632,7 +5635,7 @@
         <v>15</v>
       </c>
       <c r="AK48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:38">
@@ -5655,7 +5658,7 @@
         <v>15</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K49" s="5" t="s">
         <v>15</v>
@@ -5691,19 +5694,19 @@
         <v>15</v>
       </c>
       <c r="W49" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X49" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Z49" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA49" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB49" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD49" s="5" t="s">
         <v>15</v>
@@ -5724,7 +5727,7 @@
         <v>15</v>
       </c>
       <c r="AK49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:38">
@@ -5747,7 +5750,7 @@
         <v>15</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K50" s="5" t="s">
         <v>15</v>
@@ -5783,19 +5786,19 @@
         <v>15</v>
       </c>
       <c r="W50" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X50" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Z50" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA50" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB50" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD50" s="5" t="s">
         <v>15</v>
@@ -5816,7 +5819,7 @@
         <v>15</v>
       </c>
       <c r="AK50" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:38">
@@ -5881,13 +5884,13 @@
         <v>15</v>
       </c>
       <c r="Z51" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA51" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB51" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD51" s="5" t="s">
         <v>15</v>
@@ -5908,7 +5911,7 @@
         <v>15</v>
       </c>
       <c r="AK51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:38">
@@ -5943,7 +5946,7 @@
         <v>15</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P52" s="5" t="s">
         <v>15</v>
@@ -5961,7 +5964,7 @@
         <v>15</v>
       </c>
       <c r="U52" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V52" s="5" t="s">
         <v>15</v>
@@ -5973,19 +5976,19 @@
         <v>15</v>
       </c>
       <c r="Z52" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA52" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB52" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD52" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE52" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF52" s="5" t="s">
         <v>15</v>
@@ -6000,7 +6003,7 @@
         <v>15</v>
       </c>
       <c r="AK52" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:38">
@@ -6035,7 +6038,7 @@
         <v>15</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P53" s="5" t="s">
         <v>15</v>
@@ -6053,7 +6056,7 @@
         <v>15</v>
       </c>
       <c r="U53" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V53" s="5" t="s">
         <v>15</v>
@@ -6065,19 +6068,19 @@
         <v>15</v>
       </c>
       <c r="Z53" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA53" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB53" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD53" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE53" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF53" s="5" t="s">
         <v>15</v>
@@ -6092,7 +6095,7 @@
         <v>15</v>
       </c>
       <c r="AK53" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="1:38">
@@ -6103,7 +6106,7 @@
         <v>9</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>15</v>
@@ -6157,13 +6160,13 @@
         <v>15</v>
       </c>
       <c r="Z54" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA54" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB54" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD54" s="5" t="s">
         <v>15</v>
@@ -6181,18 +6184,18 @@
         <v>15</v>
       </c>
       <c r="AJ54" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:38">
       <c r="A56" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B56" s="1">
         <v>6</v>
@@ -6282,10 +6285,10 @@
         <v>15</v>
       </c>
       <c r="AK56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AL56" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:38">
@@ -6317,7 +6320,7 @@
         <v>15</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N57" s="5" t="s">
         <v>15</v>
@@ -6341,7 +6344,7 @@
         <v>15</v>
       </c>
       <c r="V57" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W57" s="5" t="s">
         <v>15</v>
@@ -6350,19 +6353,19 @@
         <v>15</v>
       </c>
       <c r="Z57" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA57" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB57" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD57" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE57" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF57" s="5" t="s">
         <v>15</v>
@@ -6377,7 +6380,7 @@
         <v>15</v>
       </c>
       <c r="AK57" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:38">
@@ -6409,7 +6412,7 @@
         <v>15</v>
       </c>
       <c r="M58" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N58" s="5" t="s">
         <v>15</v>
@@ -6433,7 +6436,7 @@
         <v>15</v>
       </c>
       <c r="V58" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W58" s="5" t="s">
         <v>15</v>
@@ -6442,19 +6445,19 @@
         <v>15</v>
       </c>
       <c r="Z58" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA58" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB58" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD58" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE58" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF58" s="5" t="s">
         <v>15</v>
@@ -6469,7 +6472,7 @@
         <v>15</v>
       </c>
       <c r="AK58" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:38">
@@ -6534,13 +6537,13 @@
         <v>15</v>
       </c>
       <c r="Z59" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA59" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB59" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD59" s="5" t="s">
         <v>15</v>
@@ -6561,7 +6564,7 @@
         <v>15</v>
       </c>
       <c r="AK59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:38">
@@ -6584,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K60" s="5" t="s">
         <v>15</v>
@@ -6620,19 +6623,19 @@
         <v>15</v>
       </c>
       <c r="W60" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X60" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Z60" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA60" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB60" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD60" s="5" t="s">
         <v>15</v>
@@ -6653,7 +6656,7 @@
         <v>15</v>
       </c>
       <c r="AK60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:38">
@@ -6676,7 +6679,7 @@
         <v>15</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K61" s="5" t="s">
         <v>15</v>
@@ -6712,19 +6715,19 @@
         <v>15</v>
       </c>
       <c r="W61" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X61" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Z61" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA61" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB61" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD61" s="5" t="s">
         <v>15</v>
@@ -6745,7 +6748,7 @@
         <v>15</v>
       </c>
       <c r="AK61" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:38">
@@ -6810,13 +6813,13 @@
         <v>15</v>
       </c>
       <c r="Z62" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA62" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB62" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD62" s="5" t="s">
         <v>15</v>
@@ -6837,7 +6840,7 @@
         <v>15</v>
       </c>
       <c r="AK62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:38">
@@ -6872,7 +6875,7 @@
         <v>15</v>
       </c>
       <c r="N63" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P63" s="5" t="s">
         <v>15</v>
@@ -6890,7 +6893,7 @@
         <v>15</v>
       </c>
       <c r="U63" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V63" s="5" t="s">
         <v>15</v>
@@ -6902,19 +6905,19 @@
         <v>15</v>
       </c>
       <c r="Z63" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA63" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB63" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD63" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE63" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF63" s="5" t="s">
         <v>15</v>
@@ -6929,7 +6932,7 @@
         <v>15</v>
       </c>
       <c r="AK63" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:38">
@@ -6964,7 +6967,7 @@
         <v>15</v>
       </c>
       <c r="N64" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P64" s="5" t="s">
         <v>15</v>
@@ -6982,7 +6985,7 @@
         <v>15</v>
       </c>
       <c r="U64" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V64" s="5" t="s">
         <v>15</v>
@@ -6994,19 +6997,19 @@
         <v>15</v>
       </c>
       <c r="Z64" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA64" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB64" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD64" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE64" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF64" s="5" t="s">
         <v>15</v>
@@ -7021,7 +7024,7 @@
         <v>15</v>
       </c>
       <c r="AK64" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="1:38">
@@ -7032,7 +7035,7 @@
         <v>9</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>15</v>
@@ -7086,13 +7089,13 @@
         <v>15</v>
       </c>
       <c r="Z65" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA65" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB65" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD65" s="5" t="s">
         <v>15</v>
@@ -7110,18 +7113,18 @@
         <v>15</v>
       </c>
       <c r="AJ65" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK65" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:38">
       <c r="A67" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B67" s="1">
         <v>7</v>
@@ -7211,7 +7214,7 @@
         <v>15</v>
       </c>
       <c r="AK67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:38">
@@ -7243,7 +7246,7 @@
         <v>15</v>
       </c>
       <c r="M68" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N68" s="5" t="s">
         <v>15</v>
@@ -7267,7 +7270,7 @@
         <v>15</v>
       </c>
       <c r="V68" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W68" s="5" t="s">
         <v>15</v>
@@ -7276,13 +7279,13 @@
         <v>15</v>
       </c>
       <c r="Z68" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA68" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB68" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD68" s="5" t="s">
         <v>15</v>
@@ -7291,7 +7294,7 @@
         <v>15</v>
       </c>
       <c r="AF68" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG68" s="5" t="s">
         <v>15</v>
@@ -7303,10 +7306,10 @@
         <v>15</v>
       </c>
       <c r="AK68" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AL68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:38">
@@ -7338,7 +7341,7 @@
         <v>15</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N69" s="5" t="s">
         <v>15</v>
@@ -7362,7 +7365,7 @@
         <v>15</v>
       </c>
       <c r="V69" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W69" s="5" t="s">
         <v>15</v>
@@ -7371,13 +7374,13 @@
         <v>15</v>
       </c>
       <c r="Z69" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA69" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB69" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD69" s="5" t="s">
         <v>15</v>
@@ -7386,7 +7389,7 @@
         <v>15</v>
       </c>
       <c r="AF69" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG69" s="5" t="s">
         <v>15</v>
@@ -7398,10 +7401,10 @@
         <v>15</v>
       </c>
       <c r="AK69" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL69" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:38">
@@ -7466,13 +7469,13 @@
         <v>15</v>
       </c>
       <c r="Z70" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA70" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB70" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD70" s="5" t="s">
         <v>15</v>
@@ -7493,10 +7496,10 @@
         <v>15</v>
       </c>
       <c r="AK70" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL70" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="71" spans="1:38">
@@ -7519,7 +7522,7 @@
         <v>15</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K71" s="5" t="s">
         <v>15</v>
@@ -7555,19 +7558,19 @@
         <v>15</v>
       </c>
       <c r="W71" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X71" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Z71" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA71" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB71" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD71" s="5" t="s">
         <v>15</v>
@@ -7588,10 +7591,10 @@
         <v>15</v>
       </c>
       <c r="AK71" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AL71" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="72" spans="1:38">
@@ -7614,7 +7617,7 @@
         <v>15</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K72" s="5" t="s">
         <v>15</v>
@@ -7650,19 +7653,19 @@
         <v>15</v>
       </c>
       <c r="W72" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X72" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Z72" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA72" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB72" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD72" s="5" t="s">
         <v>15</v>
@@ -7683,10 +7686,10 @@
         <v>15</v>
       </c>
       <c r="AK72" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AL72" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73" spans="1:38">
@@ -7751,13 +7754,13 @@
         <v>15</v>
       </c>
       <c r="Z73" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA73" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB73" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD73" s="5" t="s">
         <v>15</v>
@@ -7778,10 +7781,10 @@
         <v>15</v>
       </c>
       <c r="AK73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL73" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="74" spans="1:38">
@@ -7816,7 +7819,7 @@
         <v>15</v>
       </c>
       <c r="N74" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P74" s="5" t="s">
         <v>15</v>
@@ -7834,7 +7837,7 @@
         <v>15</v>
       </c>
       <c r="U74" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V74" s="5" t="s">
         <v>15</v>
@@ -7843,16 +7846,16 @@
         <v>15</v>
       </c>
       <c r="X74" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z74" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA74" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB74" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD74" s="5" t="s">
         <v>15</v>
@@ -7861,7 +7864,7 @@
         <v>15</v>
       </c>
       <c r="AF74" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG74" s="5" t="s">
         <v>15</v>
@@ -7873,10 +7876,10 @@
         <v>15</v>
       </c>
       <c r="AK74" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AL74" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="75" spans="1:38">
@@ -7911,7 +7914,7 @@
         <v>15</v>
       </c>
       <c r="N75" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P75" s="5" t="s">
         <v>15</v>
@@ -7929,7 +7932,7 @@
         <v>15</v>
       </c>
       <c r="U75" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V75" s="5" t="s">
         <v>15</v>
@@ -7938,16 +7941,16 @@
         <v>15</v>
       </c>
       <c r="X75" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z75" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA75" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB75" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD75" s="5" t="s">
         <v>15</v>
@@ -7956,7 +7959,7 @@
         <v>15</v>
       </c>
       <c r="AF75" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG75" s="5" t="s">
         <v>15</v>
@@ -7968,10 +7971,10 @@
         <v>15</v>
       </c>
       <c r="AK75" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AL75" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:38">
@@ -8036,13 +8039,13 @@
         <v>15</v>
       </c>
       <c r="Z76" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA76" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB76" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD76" s="5" t="s">
         <v>15</v>
@@ -8063,7 +8066,7 @@
         <v>15</v>
       </c>
       <c r="AK76" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77" spans="1:38">
@@ -8095,13 +8098,13 @@
         <v>15</v>
       </c>
       <c r="M77" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N77" s="5" t="s">
         <v>15</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q77" s="5" t="s">
         <v>15</v>
@@ -8128,13 +8131,13 @@
         <v>15</v>
       </c>
       <c r="Z77" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA77" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB77" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD77" s="5" t="s">
         <v>15</v>
@@ -8149,16 +8152,16 @@
         <v>15</v>
       </c>
       <c r="AH77" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ77" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AK77" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="AL77" t="s">
         <v>105</v>
-      </c>
-      <c r="AL77" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="78" spans="1:38">
@@ -8190,13 +8193,13 @@
         <v>15</v>
       </c>
       <c r="M78" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N78" s="5" t="s">
         <v>15</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q78" s="5" t="s">
         <v>15</v>
@@ -8223,13 +8226,13 @@
         <v>15</v>
       </c>
       <c r="Z78" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA78" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB78" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD78" s="5" t="s">
         <v>15</v>
@@ -8244,16 +8247,16 @@
         <v>15</v>
       </c>
       <c r="AH78" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ78" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AK78" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AL78" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="79" spans="1:38">
@@ -8318,13 +8321,13 @@
         <v>15</v>
       </c>
       <c r="Z79" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA79" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB79" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD79" s="5" t="s">
         <v>15</v>
@@ -8345,7 +8348,7 @@
         <v>15</v>
       </c>
       <c r="AK79" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80" spans="1:38">
@@ -8362,7 +8365,7 @@
         <v>15</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I80" s="5" t="s">
         <v>15</v>
@@ -8398,7 +8401,7 @@
         <v>15</v>
       </c>
       <c r="U80" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V80" s="5" t="s">
         <v>15</v>
@@ -8410,19 +8413,19 @@
         <v>15</v>
       </c>
       <c r="Z80" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA80" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB80" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD80" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE80" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF80" s="5" t="s">
         <v>15</v>
@@ -8437,10 +8440,10 @@
         <v>15</v>
       </c>
       <c r="AK80" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AL80" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="81" spans="1:38">
@@ -8457,7 +8460,7 @@
         <v>15</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I81" s="5" t="s">
         <v>15</v>
@@ -8493,7 +8496,7 @@
         <v>15</v>
       </c>
       <c r="U81" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V81" s="5" t="s">
         <v>15</v>
@@ -8505,19 +8508,19 @@
         <v>15</v>
       </c>
       <c r="Z81" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA81" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB81" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD81" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE81" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF81" s="5" t="s">
         <v>15</v>
@@ -8532,10 +8535,10 @@
         <v>15</v>
       </c>
       <c r="AK81" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AL81" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82" spans="1:38">
@@ -8546,7 +8549,7 @@
         <v>15</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>15</v>
@@ -8600,13 +8603,13 @@
         <v>15</v>
       </c>
       <c r="Z82" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA82" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB82" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD82" s="5" t="s">
         <v>15</v>
@@ -8624,18 +8627,18 @@
         <v>15</v>
       </c>
       <c r="AJ82" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK82" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL82" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:38">
       <c r="A84" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B84" s="1">
         <v>8</v>
@@ -8725,7 +8728,7 @@
         <v>15</v>
       </c>
       <c r="AK84" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="85" spans="1:38">
@@ -8757,13 +8760,13 @@
         <v>15</v>
       </c>
       <c r="M85" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N85" s="5" t="s">
         <v>15</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q85" s="5" t="s">
         <v>15</v>
@@ -8790,19 +8793,19 @@
         <v>15</v>
       </c>
       <c r="Z85" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA85" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB85" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD85" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE85" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF85" s="5" t="s">
         <v>15</v>
@@ -8817,10 +8820,10 @@
         <v>15</v>
       </c>
       <c r="AK85" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AL85" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="86" spans="1:38">
@@ -8852,13 +8855,13 @@
         <v>15</v>
       </c>
       <c r="M86" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N86" s="5" t="s">
         <v>15</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q86" s="5" t="s">
         <v>15</v>
@@ -8885,19 +8888,19 @@
         <v>15</v>
       </c>
       <c r="Z86" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA86" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB86" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD86" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE86" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF86" s="5" t="s">
         <v>15</v>
@@ -8912,10 +8915,10 @@
         <v>15</v>
       </c>
       <c r="AK86" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AL86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="87" spans="1:38">
@@ -8980,13 +8983,13 @@
         <v>15</v>
       </c>
       <c r="Z87" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA87" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB87" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD87" s="5" t="s">
         <v>15</v>
@@ -9007,7 +9010,7 @@
         <v>15</v>
       </c>
       <c r="AK87" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88" spans="1:38">
@@ -9039,7 +9042,7 @@
         <v>15</v>
       </c>
       <c r="M88" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N88" s="5" t="s">
         <v>15</v>
@@ -9048,7 +9051,7 @@
         <v>15</v>
       </c>
       <c r="Q88" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R88" s="5" t="s">
         <v>15</v>
@@ -9072,13 +9075,13 @@
         <v>15</v>
       </c>
       <c r="Z88" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA88" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB88" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD88" s="5" t="s">
         <v>15</v>
@@ -9087,7 +9090,7 @@
         <v>15</v>
       </c>
       <c r="AF88" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG88" s="5" t="s">
         <v>15</v>
@@ -9099,10 +9102,10 @@
         <v>15</v>
       </c>
       <c r="AK88" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="AL88" t="s">
         <v>111</v>
-      </c>
-      <c r="AL88" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="89" spans="1:38">
@@ -9134,7 +9137,7 @@
         <v>15</v>
       </c>
       <c r="M89" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N89" s="5" t="s">
         <v>15</v>
@@ -9143,7 +9146,7 @@
         <v>15</v>
       </c>
       <c r="Q89" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R89" s="5" t="s">
         <v>15</v>
@@ -9167,13 +9170,13 @@
         <v>15</v>
       </c>
       <c r="Z89" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA89" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB89" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD89" s="5" t="s">
         <v>15</v>
@@ -9182,7 +9185,7 @@
         <v>15</v>
       </c>
       <c r="AF89" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG89" s="5" t="s">
         <v>15</v>
@@ -9194,10 +9197,10 @@
         <v>15</v>
       </c>
       <c r="AK89" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AL89" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="90" spans="1:38">
@@ -9262,13 +9265,13 @@
         <v>15</v>
       </c>
       <c r="Z90" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA90" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB90" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD90" s="5" t="s">
         <v>15</v>
@@ -9289,7 +9292,7 @@
         <v>15</v>
       </c>
       <c r="AK90" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91" spans="1:38">
@@ -9309,7 +9312,7 @@
         <v>15</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J91" s="5" t="s">
         <v>15</v>
@@ -9342,7 +9345,7 @@
         <v>15</v>
       </c>
       <c r="U91" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V91" s="5" t="s">
         <v>15</v>
@@ -9354,13 +9357,13 @@
         <v>15</v>
       </c>
       <c r="Z91" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA91" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB91" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD91" s="5" t="s">
         <v>15</v>
@@ -9372,7 +9375,7 @@
         <v>15</v>
       </c>
       <c r="AG91" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH91" s="5" t="s">
         <v>15</v>
@@ -9381,10 +9384,10 @@
         <v>15</v>
       </c>
       <c r="AK91" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AL91" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="92" spans="1:38">
@@ -9404,7 +9407,7 @@
         <v>15</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J92" s="5" t="s">
         <v>15</v>
@@ -9437,7 +9440,7 @@
         <v>15</v>
       </c>
       <c r="U92" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V92" s="5" t="s">
         <v>15</v>
@@ -9449,13 +9452,13 @@
         <v>15</v>
       </c>
       <c r="Z92" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA92" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB92" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD92" s="5" t="s">
         <v>15</v>
@@ -9467,7 +9470,7 @@
         <v>15</v>
       </c>
       <c r="AG92" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH92" s="5" t="s">
         <v>15</v>
@@ -9476,10 +9479,10 @@
         <v>15</v>
       </c>
       <c r="AK92" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AL92" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="93" spans="1:38">
@@ -9544,13 +9547,13 @@
         <v>15</v>
       </c>
       <c r="Z93" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA93" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB93" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD93" s="5" t="s">
         <v>15</v>
@@ -9571,7 +9574,7 @@
         <v>15</v>
       </c>
       <c r="AK93" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="94" spans="1:38">
@@ -9591,7 +9594,7 @@
         <v>15</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J94" s="5" t="s">
         <v>15</v>
@@ -9627,7 +9630,7 @@
         <v>15</v>
       </c>
       <c r="V94" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W94" s="5" t="s">
         <v>15</v>
@@ -9636,13 +9639,13 @@
         <v>15</v>
       </c>
       <c r="Z94" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA94" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB94" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD94" s="5" t="s">
         <v>15</v>
@@ -9663,10 +9666,10 @@
         <v>15</v>
       </c>
       <c r="AK94" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AL94" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="95" spans="1:38">
@@ -9686,7 +9689,7 @@
         <v>15</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J95" s="5" t="s">
         <v>15</v>
@@ -9722,7 +9725,7 @@
         <v>15</v>
       </c>
       <c r="V95" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W95" s="5" t="s">
         <v>15</v>
@@ -9731,13 +9734,13 @@
         <v>15</v>
       </c>
       <c r="Z95" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA95" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB95" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD95" s="5" t="s">
         <v>15</v>
@@ -9758,10 +9761,10 @@
         <v>15</v>
       </c>
       <c r="AK95" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL95" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="96" spans="1:38">
@@ -9826,13 +9829,13 @@
         <v>15</v>
       </c>
       <c r="Z96" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA96" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB96" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD96" s="5" t="s">
         <v>15</v>
@@ -9853,10 +9856,10 @@
         <v>15</v>
       </c>
       <c r="AK96" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL96" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97" spans="1:38">
@@ -9879,7 +9882,7 @@
         <v>15</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K97" s="5" t="s">
         <v>15</v>
@@ -9915,19 +9918,19 @@
         <v>15</v>
       </c>
       <c r="W97" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X97" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Z97" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA97" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB97" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD97" s="5" t="s">
         <v>15</v>
@@ -9948,10 +9951,10 @@
         <v>15</v>
       </c>
       <c r="AK97" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AL97" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="98" spans="1:38">
@@ -9974,7 +9977,7 @@
         <v>15</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K98" s="5" t="s">
         <v>15</v>
@@ -10010,19 +10013,19 @@
         <v>15</v>
       </c>
       <c r="W98" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X98" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Z98" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA98" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB98" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD98" s="5" t="s">
         <v>15</v>
@@ -10043,10 +10046,10 @@
         <v>15</v>
       </c>
       <c r="AK98" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AL98" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="99" spans="1:38">
@@ -10111,13 +10114,13 @@
         <v>15</v>
       </c>
       <c r="Z99" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA99" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB99" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD99" s="5" t="s">
         <v>15</v>
@@ -10138,10 +10141,10 @@
         <v>15</v>
       </c>
       <c r="AK99" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:38">
@@ -10176,7 +10179,7 @@
         <v>15</v>
       </c>
       <c r="N100" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P100" s="5" t="s">
         <v>15</v>
@@ -10194,7 +10197,7 @@
         <v>15</v>
       </c>
       <c r="U100" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V100" s="5" t="s">
         <v>15</v>
@@ -10206,13 +10209,13 @@
         <v>15</v>
       </c>
       <c r="Z100" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA100" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB100" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD100" s="5" t="s">
         <v>15</v>
@@ -10221,7 +10224,7 @@
         <v>15</v>
       </c>
       <c r="AF100" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG100" s="5" t="s">
         <v>15</v>
@@ -10233,10 +10236,10 @@
         <v>15</v>
       </c>
       <c r="AK100" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AL100" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101" spans="1:38">
@@ -10271,7 +10274,7 @@
         <v>15</v>
       </c>
       <c r="N101" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P101" s="5" t="s">
         <v>15</v>
@@ -10289,7 +10292,7 @@
         <v>15</v>
       </c>
       <c r="U101" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V101" s="5" t="s">
         <v>15</v>
@@ -10301,13 +10304,13 @@
         <v>15</v>
       </c>
       <c r="Z101" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA101" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB101" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD101" s="5" t="s">
         <v>15</v>
@@ -10316,7 +10319,7 @@
         <v>15</v>
       </c>
       <c r="AF101" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG101" s="5" t="s">
         <v>15</v>
@@ -10328,10 +10331,10 @@
         <v>15</v>
       </c>
       <c r="AK101" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AL101" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="102" spans="1:38">
@@ -10342,7 +10345,7 @@
         <v>18</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>15</v>
@@ -10396,13 +10399,13 @@
         <v>15</v>
       </c>
       <c r="Z102" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA102" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB102" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD102" s="5" t="s">
         <v>15</v>
@@ -10420,18 +10423,18 @@
         <v>15</v>
       </c>
       <c r="AJ102" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK102" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL102" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104" spans="1:38">
       <c r="A104" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B104" s="1">
         <v>9</v>
@@ -10521,10 +10524,10 @@
         <v>15</v>
       </c>
       <c r="AK104" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AL104" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="105" spans="1:38">
@@ -10535,7 +10538,7 @@
         <v>1</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G105" s="5" t="s">
         <v>15</v>
@@ -10556,7 +10559,7 @@
         <v>15</v>
       </c>
       <c r="M105" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N105" s="5" t="s">
         <v>15</v>
@@ -10565,7 +10568,7 @@
         <v>15</v>
       </c>
       <c r="Q105" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R105" s="5" t="s">
         <v>15</v>
@@ -10589,13 +10592,13 @@
         <v>15</v>
       </c>
       <c r="Z105" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA105" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB105" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD105" s="5" t="s">
         <v>15</v>
@@ -10604,7 +10607,7 @@
         <v>15</v>
       </c>
       <c r="AF105" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG105" s="5" t="s">
         <v>15</v>
@@ -10616,10 +10619,10 @@
         <v>15</v>
       </c>
       <c r="AK105" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AL105" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="106" spans="1:38">
@@ -10651,7 +10654,7 @@
         <v>15</v>
       </c>
       <c r="M106" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N106" s="5" t="s">
         <v>15</v>
@@ -10660,7 +10663,7 @@
         <v>15</v>
       </c>
       <c r="Q106" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R106" s="5" t="s">
         <v>15</v>
@@ -10684,13 +10687,13 @@
         <v>15</v>
       </c>
       <c r="Z106" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA106" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB106" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD106" s="5" t="s">
         <v>15</v>
@@ -10699,7 +10702,7 @@
         <v>15</v>
       </c>
       <c r="AF106" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG106" s="5" t="s">
         <v>15</v>
@@ -10711,10 +10714,10 @@
         <v>15</v>
       </c>
       <c r="AK106" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AL106" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107" spans="1:38">
@@ -10779,13 +10782,13 @@
         <v>15</v>
       </c>
       <c r="Z107" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA107" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB107" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD107" s="5" t="s">
         <v>15</v>
@@ -10806,7 +10809,7 @@
         <v>15</v>
       </c>
       <c r="AK107" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108" spans="1:38">
@@ -10832,7 +10835,7 @@
         <v>15</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L108" s="5" t="s">
         <v>15</v>
@@ -10859,7 +10862,7 @@
         <v>15</v>
       </c>
       <c r="U108" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V108" s="5" t="s">
         <v>15</v>
@@ -10871,13 +10874,13 @@
         <v>15</v>
       </c>
       <c r="Z108" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA108" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB108" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD108" s="5" t="s">
         <v>15</v>
@@ -10889,7 +10892,7 @@
         <v>15</v>
       </c>
       <c r="AG108" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH108" s="5" t="s">
         <v>15</v>
@@ -10898,10 +10901,10 @@
         <v>15</v>
       </c>
       <c r="AK108" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="AL108" t="s">
         <v>123</v>
-      </c>
-      <c r="AL108" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="109" spans="1:38">
@@ -10927,7 +10930,7 @@
         <v>15</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L109" s="5" t="s">
         <v>15</v>
@@ -10954,7 +10957,7 @@
         <v>15</v>
       </c>
       <c r="U109" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V109" s="5" t="s">
         <v>15</v>
@@ -10966,13 +10969,13 @@
         <v>15</v>
       </c>
       <c r="Z109" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA109" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB109" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD109" s="5" t="s">
         <v>15</v>
@@ -10993,10 +10996,10 @@
         <v>15</v>
       </c>
       <c r="AK109" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AL109" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="110" spans="1:38">
@@ -11061,13 +11064,13 @@
         <v>15</v>
       </c>
       <c r="Z110" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA110" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB110" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD110" s="5" t="s">
         <v>15</v>
@@ -11088,7 +11091,7 @@
         <v>15</v>
       </c>
       <c r="AK110" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="111" spans="1:38">
@@ -11108,7 +11111,7 @@
         <v>15</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J111" s="5" t="s">
         <v>15</v>
@@ -11144,7 +11147,7 @@
         <v>15</v>
       </c>
       <c r="V111" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W111" s="5" t="s">
         <v>15</v>
@@ -11153,13 +11156,13 @@
         <v>15</v>
       </c>
       <c r="Z111" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA111" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB111" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD111" s="5" t="s">
         <v>15</v>
@@ -11180,10 +11183,10 @@
         <v>15</v>
       </c>
       <c r="AK111" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AL111" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="112" spans="1:38">
@@ -11203,7 +11206,7 @@
         <v>15</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J112" s="5" t="s">
         <v>15</v>
@@ -11239,7 +11242,7 @@
         <v>15</v>
       </c>
       <c r="V112" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W112" s="5" t="s">
         <v>15</v>
@@ -11248,13 +11251,13 @@
         <v>15</v>
       </c>
       <c r="Z112" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA112" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB112" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD112" s="5" t="s">
         <v>15</v>
@@ -11275,10 +11278,10 @@
         <v>15</v>
       </c>
       <c r="AK112" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL112" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="113" spans="1:38">
@@ -11343,13 +11346,13 @@
         <v>15</v>
       </c>
       <c r="Z113" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA113" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB113" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD113" s="5" t="s">
         <v>15</v>
@@ -11370,10 +11373,10 @@
         <v>15</v>
       </c>
       <c r="AK113" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL113" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="114" spans="1:38">
@@ -11396,7 +11399,7 @@
         <v>15</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K114" s="5" t="s">
         <v>15</v>
@@ -11432,19 +11435,19 @@
         <v>15</v>
       </c>
       <c r="W114" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X114" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Z114" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA114" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB114" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD114" s="5" t="s">
         <v>15</v>
@@ -11465,10 +11468,10 @@
         <v>15</v>
       </c>
       <c r="AK114" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AL114" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="115" spans="1:38">
@@ -11491,7 +11494,7 @@
         <v>15</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K115" s="5" t="s">
         <v>15</v>
@@ -11527,19 +11530,19 @@
         <v>15</v>
       </c>
       <c r="W115" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X115" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Z115" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA115" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB115" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD115" s="5" t="s">
         <v>15</v>
@@ -11560,10 +11563,10 @@
         <v>15</v>
       </c>
       <c r="AK115" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AL115" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="116" spans="1:38">
@@ -11628,13 +11631,13 @@
         <v>15</v>
       </c>
       <c r="Z116" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA116" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB116" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD116" s="5" t="s">
         <v>15</v>
@@ -11655,10 +11658,10 @@
         <v>15</v>
       </c>
       <c r="AK116" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL116" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="117" spans="1:38">
@@ -11693,7 +11696,7 @@
         <v>15</v>
       </c>
       <c r="N117" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P117" s="5" t="s">
         <v>15</v>
@@ -11711,7 +11714,7 @@
         <v>15</v>
       </c>
       <c r="U117" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V117" s="5" t="s">
         <v>15</v>
@@ -11723,13 +11726,13 @@
         <v>15</v>
       </c>
       <c r="Z117" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA117" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB117" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD117" s="5" t="s">
         <v>15</v>
@@ -11738,7 +11741,7 @@
         <v>15</v>
       </c>
       <c r="AF117" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG117" s="5" t="s">
         <v>15</v>
@@ -11750,10 +11753,10 @@
         <v>15</v>
       </c>
       <c r="AK117" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AL117" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="118" spans="1:38">
@@ -11788,7 +11791,7 @@
         <v>15</v>
       </c>
       <c r="N118" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P118" s="5" t="s">
         <v>15</v>
@@ -11806,7 +11809,7 @@
         <v>15</v>
       </c>
       <c r="U118" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V118" s="5" t="s">
         <v>15</v>
@@ -11818,13 +11821,13 @@
         <v>15</v>
       </c>
       <c r="Z118" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA118" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB118" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD118" s="5" t="s">
         <v>15</v>
@@ -11833,7 +11836,7 @@
         <v>15</v>
       </c>
       <c r="AF118" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG118" s="5" t="s">
         <v>15</v>
@@ -11845,10 +11848,10 @@
         <v>15</v>
       </c>
       <c r="AK118" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AL118" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="119" spans="1:38">
@@ -11913,13 +11916,13 @@
         <v>15</v>
       </c>
       <c r="Z119" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA119" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB119" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD119" s="5" t="s">
         <v>15</v>
@@ -11937,18 +11940,18 @@
         <v>15</v>
       </c>
       <c r="AJ119" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK119" t="s">
         <v>18</v>
       </c>
-      <c r="AK119" t="s">
-        <v>19</v>
-      </c>
       <c r="AL119" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="121" spans="1:38">
       <c r="A121" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B121" s="1">
         <v>10</v>
@@ -12038,7 +12041,7 @@
         <v>15</v>
       </c>
       <c r="AK121" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="122" spans="1:38">
@@ -12070,7 +12073,7 @@
         <v>15</v>
       </c>
       <c r="M122" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N122" s="5" t="s">
         <v>15</v>
@@ -12094,7 +12097,7 @@
         <v>15</v>
       </c>
       <c r="V122" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W122" s="5" t="s">
         <v>15</v>
@@ -12103,13 +12106,13 @@
         <v>15</v>
       </c>
       <c r="Z122" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA122" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB122" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD122" s="5" t="s">
         <v>15</v>
@@ -12118,7 +12121,7 @@
         <v>15</v>
       </c>
       <c r="AF122" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG122" s="5" t="s">
         <v>15</v>
@@ -12130,10 +12133,10 @@
         <v>15</v>
       </c>
       <c r="AK122" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AL122" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="123" spans="1:38">
@@ -12165,7 +12168,7 @@
         <v>15</v>
       </c>
       <c r="M123" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N123" s="5" t="s">
         <v>15</v>
@@ -12189,7 +12192,7 @@
         <v>15</v>
       </c>
       <c r="V123" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W123" s="5" t="s">
         <v>15</v>
@@ -12198,13 +12201,13 @@
         <v>15</v>
       </c>
       <c r="Z123" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA123" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB123" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD123" s="5" t="s">
         <v>15</v>
@@ -12213,7 +12216,7 @@
         <v>15</v>
       </c>
       <c r="AF123" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG123" s="5" t="s">
         <v>15</v>
@@ -12225,10 +12228,10 @@
         <v>15</v>
       </c>
       <c r="AK123" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL123" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="124" spans="1:38">
@@ -12293,13 +12296,13 @@
         <v>15</v>
       </c>
       <c r="Z124" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA124" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB124" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD124" s="5" t="s">
         <v>15</v>
@@ -12320,10 +12323,10 @@
         <v>15</v>
       </c>
       <c r="AK124" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL124" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="125" spans="1:38">
@@ -12346,7 +12349,7 @@
         <v>15</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K125" s="5" t="s">
         <v>15</v>
@@ -12382,19 +12385,19 @@
         <v>15</v>
       </c>
       <c r="W125" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X125" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Z125" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA125" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB125" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD125" s="5" t="s">
         <v>15</v>
@@ -12415,10 +12418,10 @@
         <v>15</v>
       </c>
       <c r="AK125" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AL125" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="126" spans="1:38">
@@ -12441,7 +12444,7 @@
         <v>15</v>
       </c>
       <c r="J126" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K126" s="5" t="s">
         <v>15</v>
@@ -12477,19 +12480,19 @@
         <v>15</v>
       </c>
       <c r="W126" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X126" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Z126" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA126" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB126" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD126" s="5" t="s">
         <v>15</v>
@@ -12510,10 +12513,10 @@
         <v>15</v>
       </c>
       <c r="AK126" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AL126" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="127" spans="1:38">
@@ -12578,13 +12581,13 @@
         <v>15</v>
       </c>
       <c r="Z127" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA127" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB127" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD127" s="5" t="s">
         <v>15</v>
@@ -12605,10 +12608,10 @@
         <v>15</v>
       </c>
       <c r="AK127" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL127" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="128" spans="1:38">
@@ -12643,7 +12646,7 @@
         <v>15</v>
       </c>
       <c r="N128" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P128" s="5" t="s">
         <v>15</v>
@@ -12661,7 +12664,7 @@
         <v>15</v>
       </c>
       <c r="U128" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V128" s="5" t="s">
         <v>15</v>
@@ -12670,16 +12673,16 @@
         <v>15</v>
       </c>
       <c r="X128" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z128" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA128" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB128" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD128" s="5" t="s">
         <v>15</v>
@@ -12688,7 +12691,7 @@
         <v>15</v>
       </c>
       <c r="AF128" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG128" s="5" t="s">
         <v>15</v>
@@ -12700,10 +12703,10 @@
         <v>15</v>
       </c>
       <c r="AK128" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AL128" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="129" spans="1:38">
@@ -12738,7 +12741,7 @@
         <v>15</v>
       </c>
       <c r="N129" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P129" s="5" t="s">
         <v>15</v>
@@ -12756,7 +12759,7 @@
         <v>15</v>
       </c>
       <c r="U129" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V129" s="5" t="s">
         <v>15</v>
@@ -12765,16 +12768,16 @@
         <v>15</v>
       </c>
       <c r="X129" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z129" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA129" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB129" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD129" s="5" t="s">
         <v>15</v>
@@ -12783,7 +12786,7 @@
         <v>15</v>
       </c>
       <c r="AF129" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG129" s="5" t="s">
         <v>15</v>
@@ -12795,10 +12798,10 @@
         <v>15</v>
       </c>
       <c r="AK129" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AL129" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="130" spans="1:38">
@@ -12863,13 +12866,13 @@
         <v>15</v>
       </c>
       <c r="Z130" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA130" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB130" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD130" s="5" t="s">
         <v>15</v>
@@ -12890,7 +12893,7 @@
         <v>15</v>
       </c>
       <c r="AK130" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131" spans="1:38">
@@ -12922,7 +12925,7 @@
         <v>15</v>
       </c>
       <c r="M131" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N131" s="5" t="s">
         <v>15</v>
@@ -12934,7 +12937,7 @@
         <v>15</v>
       </c>
       <c r="R131" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S131" s="5" t="s">
         <v>15</v>
@@ -12955,13 +12958,13 @@
         <v>15</v>
       </c>
       <c r="Z131" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA131" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB131" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD131" s="5" t="s">
         <v>15</v>
@@ -12976,16 +12979,16 @@
         <v>15</v>
       </c>
       <c r="AH131" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ131" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AK131" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AL131" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="132" spans="1:38">
@@ -13017,7 +13020,7 @@
         <v>15</v>
       </c>
       <c r="M132" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N132" s="5" t="s">
         <v>15</v>
@@ -13029,7 +13032,7 @@
         <v>15</v>
       </c>
       <c r="R132" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S132" s="5" t="s">
         <v>15</v>
@@ -13050,13 +13053,13 @@
         <v>15</v>
       </c>
       <c r="Z132" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA132" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB132" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD132" s="5" t="s">
         <v>15</v>
@@ -13071,16 +13074,16 @@
         <v>15</v>
       </c>
       <c r="AH132" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ132" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AK132" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AL132" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="133" spans="1:38">
@@ -13145,13 +13148,13 @@
         <v>15</v>
       </c>
       <c r="Z133" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA133" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB133" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD133" s="5" t="s">
         <v>15</v>
@@ -13169,18 +13172,18 @@
         <v>15</v>
       </c>
       <c r="AJ133" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK133" t="s">
         <v>18</v>
       </c>
-      <c r="AK133" t="s">
-        <v>19</v>
-      </c>
       <c r="AL133" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="135" spans="1:38">
       <c r="A135" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B135" s="1">
         <v>11</v>
@@ -13270,7 +13273,7 @@
         <v>15</v>
       </c>
       <c r="AK135" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="136" spans="1:38">
@@ -13281,7 +13284,7 @@
         <v>1</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G136" s="5" t="s">
         <v>15</v>
@@ -13302,13 +13305,13 @@
         <v>15</v>
       </c>
       <c r="M136" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N136" s="5" t="s">
         <v>15</v>
       </c>
       <c r="P136" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q136" s="5" t="s">
         <v>15</v>
@@ -13347,7 +13350,7 @@
         <v>15</v>
       </c>
       <c r="AE136" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF136" s="5" t="s">
         <v>15</v>
@@ -13362,10 +13365,10 @@
         <v>15</v>
       </c>
       <c r="AK136" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AL136" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="137" spans="1:38">
@@ -13397,13 +13400,13 @@
         <v>15</v>
       </c>
       <c r="M137" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N137" s="5" t="s">
         <v>15</v>
       </c>
       <c r="P137" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q137" s="5" t="s">
         <v>15</v>
@@ -13442,7 +13445,7 @@
         <v>15</v>
       </c>
       <c r="AE137" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF137" s="5" t="s">
         <v>15</v>
@@ -13457,10 +13460,10 @@
         <v>15</v>
       </c>
       <c r="AK137" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AL137" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="138" spans="1:38">
@@ -13552,7 +13555,7 @@
         <v>15</v>
       </c>
       <c r="AK138" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139" spans="1:38">
@@ -13569,7 +13572,7 @@
         <v>15</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I139" s="5" t="s">
         <v>15</v>
@@ -13605,7 +13608,7 @@
         <v>15</v>
       </c>
       <c r="U139" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V139" s="5" t="s">
         <v>15</v>
@@ -13626,7 +13629,7 @@
         <v>16</v>
       </c>
       <c r="AD139" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE139" s="5" t="s">
         <v>15</v>
@@ -13644,10 +13647,10 @@
         <v>15</v>
       </c>
       <c r="AK139" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AL139" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="140" spans="1:38">
@@ -13664,7 +13667,7 @@
         <v>15</v>
       </c>
       <c r="H140" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I140" s="5" t="s">
         <v>15</v>
@@ -13700,7 +13703,7 @@
         <v>15</v>
       </c>
       <c r="U140" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V140" s="5" t="s">
         <v>15</v>
@@ -13721,7 +13724,7 @@
         <v>16</v>
       </c>
       <c r="AD140" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE140" s="5" t="s">
         <v>15</v>
@@ -13739,10 +13742,10 @@
         <v>15</v>
       </c>
       <c r="AK140" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AL140" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="141" spans="1:38">
@@ -13753,7 +13756,7 @@
         <v>6</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G141" s="5" t="s">
         <v>15</v>
@@ -13831,18 +13834,18 @@
         <v>15</v>
       </c>
       <c r="AJ141" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK141" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL141" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143" spans="1:38">
       <c r="A143" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B143" s="1">
         <v>12</v>
@@ -13932,7 +13935,7 @@
         <v>15</v>
       </c>
       <c r="AK143" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="144" spans="1:38">
@@ -13943,7 +13946,7 @@
         <v>1</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G144" s="5" t="s">
         <v>15</v>
@@ -13964,13 +13967,13 @@
         <v>15</v>
       </c>
       <c r="M144" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N144" s="5" t="s">
         <v>15</v>
       </c>
       <c r="P144" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q144" s="5" t="s">
         <v>15</v>
@@ -14006,7 +14009,7 @@
         <v>16</v>
       </c>
       <c r="AD144" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE144" s="5" t="s">
         <v>15</v>
@@ -14024,10 +14027,10 @@
         <v>15</v>
       </c>
       <c r="AK144" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AL144" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="145" spans="1:38">
@@ -14059,13 +14062,13 @@
         <v>15</v>
       </c>
       <c r="M145" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N145" s="5" t="s">
         <v>15</v>
       </c>
       <c r="P145" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q145" s="5" t="s">
         <v>15</v>
@@ -14101,7 +14104,7 @@
         <v>16</v>
       </c>
       <c r="AD145" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE145" s="5" t="s">
         <v>15</v>
@@ -14119,10 +14122,10 @@
         <v>15</v>
       </c>
       <c r="AK145" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AL145" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="146" spans="1:38">
@@ -14214,7 +14217,7 @@
         <v>15</v>
       </c>
       <c r="AK146" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="147" spans="1:38">
@@ -14231,7 +14234,7 @@
         <v>15</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I147" s="5" t="s">
         <v>15</v>
@@ -14267,7 +14270,7 @@
         <v>15</v>
       </c>
       <c r="U147" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V147" s="5" t="s">
         <v>15</v>
@@ -14291,7 +14294,7 @@
         <v>15</v>
       </c>
       <c r="AE147" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF147" s="5" t="s">
         <v>15</v>
@@ -14306,10 +14309,10 @@
         <v>15</v>
       </c>
       <c r="AK147" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AL147" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="148" spans="1:38">
@@ -14326,7 +14329,7 @@
         <v>15</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I148" s="5" t="s">
         <v>15</v>
@@ -14362,7 +14365,7 @@
         <v>15</v>
       </c>
       <c r="U148" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V148" s="5" t="s">
         <v>15</v>
@@ -14386,7 +14389,7 @@
         <v>15</v>
       </c>
       <c r="AE148" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF148" s="5" t="s">
         <v>15</v>
@@ -14401,10 +14404,10 @@
         <v>15</v>
       </c>
       <c r="AK148" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AL148" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="149" spans="1:38">
@@ -14415,7 +14418,7 @@
         <v>6</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G149" s="5" t="s">
         <v>15</v>
@@ -14493,18 +14496,18 @@
         <v>15</v>
       </c>
       <c r="AJ149" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK149" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL149" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="151" spans="1:38">
       <c r="A151" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B151" s="1">
         <v>13</v>
@@ -14594,7 +14597,7 @@
         <v>15</v>
       </c>
       <c r="AK151" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="152" spans="1:38">
@@ -14605,7 +14608,7 @@
         <v>1</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G152" s="5" t="s">
         <v>15</v>
@@ -14683,18 +14686,18 @@
         <v>15</v>
       </c>
       <c r="AJ152" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK152" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL152" t="s">
         <v>20</v>
-      </c>
-      <c r="AL152" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="154" spans="1:38">
       <c r="A154" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B154" s="1">
         <v>14</v>
@@ -14784,7 +14787,7 @@
         <v>15</v>
       </c>
       <c r="AK154" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="155" spans="1:38">
@@ -14816,7 +14819,7 @@
         <v>15</v>
       </c>
       <c r="M155" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N155" s="5" t="s">
         <v>15</v>
@@ -14831,7 +14834,7 @@
         <v>15</v>
       </c>
       <c r="S155" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T155" s="5" t="s">
         <v>15</v>
@@ -14861,7 +14864,7 @@
         <v>15</v>
       </c>
       <c r="AE155" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF155" s="5" t="s">
         <v>15</v>
@@ -14876,7 +14879,7 @@
         <v>15</v>
       </c>
       <c r="AK155" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="156" spans="1:38">
@@ -14908,7 +14911,7 @@
         <v>15</v>
       </c>
       <c r="M156" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N156" s="5" t="s">
         <v>15</v>
@@ -14923,7 +14926,7 @@
         <v>15</v>
       </c>
       <c r="S156" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T156" s="5" t="s">
         <v>15</v>
@@ -14953,7 +14956,7 @@
         <v>15</v>
       </c>
       <c r="AE156" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF156" s="5" t="s">
         <v>15</v>
@@ -14968,7 +14971,7 @@
         <v>15</v>
       </c>
       <c r="AK156" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="157" spans="1:38">
@@ -15060,7 +15063,7 @@
         <v>15</v>
       </c>
       <c r="AK157" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="158" spans="1:38">
@@ -15092,7 +15095,7 @@
         <v>15</v>
       </c>
       <c r="M158" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N158" s="5" t="s">
         <v>15</v>
@@ -15110,7 +15113,7 @@
         <v>15</v>
       </c>
       <c r="T158" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U158" s="5" t="s">
         <v>15</v>
@@ -15140,7 +15143,7 @@
         <v>15</v>
       </c>
       <c r="AF158" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG158" s="5" t="s">
         <v>15</v>
@@ -15152,7 +15155,7 @@
         <v>15</v>
       </c>
       <c r="AK158" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="159" spans="1:38">
@@ -15184,7 +15187,7 @@
         <v>15</v>
       </c>
       <c r="M159" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N159" s="5" t="s">
         <v>15</v>
@@ -15202,7 +15205,7 @@
         <v>15</v>
       </c>
       <c r="T159" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U159" s="5" t="s">
         <v>15</v>
@@ -15232,7 +15235,7 @@
         <v>15</v>
       </c>
       <c r="AF159" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG159" s="5" t="s">
         <v>15</v>
@@ -15244,7 +15247,7 @@
         <v>15</v>
       </c>
       <c r="AK159" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="160" spans="1:38">
@@ -15255,7 +15258,7 @@
         <v>6</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G160" s="5" t="s">
         <v>15</v>
@@ -15333,18 +15336,18 @@
         <v>15</v>
       </c>
       <c r="AJ160" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK160" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL160" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="162" spans="1:38">
       <c r="A162" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B162" s="1">
         <v>15</v>
@@ -15434,7 +15437,7 @@
         <v>15</v>
       </c>
       <c r="AK162" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="163" spans="1:38">
@@ -15466,7 +15469,7 @@
         <v>15</v>
       </c>
       <c r="M163" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N163" s="5" t="s">
         <v>15</v>
@@ -15481,7 +15484,7 @@
         <v>15</v>
       </c>
       <c r="S163" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T163" s="5" t="s">
         <v>15</v>
@@ -15511,7 +15514,7 @@
         <v>15</v>
       </c>
       <c r="AE163" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF163" s="5" t="s">
         <v>15</v>
@@ -15526,7 +15529,7 @@
         <v>15</v>
       </c>
       <c r="AK163" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="164" spans="1:38">
@@ -15558,7 +15561,7 @@
         <v>15</v>
       </c>
       <c r="M164" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N164" s="5" t="s">
         <v>15</v>
@@ -15573,7 +15576,7 @@
         <v>15</v>
       </c>
       <c r="S164" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T164" s="5" t="s">
         <v>15</v>
@@ -15603,7 +15606,7 @@
         <v>15</v>
       </c>
       <c r="AE164" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF164" s="5" t="s">
         <v>15</v>
@@ -15618,7 +15621,7 @@
         <v>15</v>
       </c>
       <c r="AK164" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="165" spans="1:38">
@@ -15710,7 +15713,7 @@
         <v>15</v>
       </c>
       <c r="AK165" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="166" spans="1:38">
@@ -15739,7 +15742,7 @@
         <v>15</v>
       </c>
       <c r="L166" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M166" s="5" t="s">
         <v>15</v>
@@ -15763,7 +15766,7 @@
         <v>15</v>
       </c>
       <c r="U166" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V166" s="5" t="s">
         <v>15</v>
@@ -15790,7 +15793,7 @@
         <v>15</v>
       </c>
       <c r="AF166" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG166" s="5" t="s">
         <v>15</v>
@@ -15802,7 +15805,7 @@
         <v>15</v>
       </c>
       <c r="AK166" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="167" spans="1:38">
@@ -15831,7 +15834,7 @@
         <v>15</v>
       </c>
       <c r="L167" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M167" s="5" t="s">
         <v>15</v>
@@ -15855,7 +15858,7 @@
         <v>15</v>
       </c>
       <c r="U167" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V167" s="5" t="s">
         <v>15</v>
@@ -15882,7 +15885,7 @@
         <v>15</v>
       </c>
       <c r="AF167" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG167" s="5" t="s">
         <v>15</v>
@@ -15894,7 +15897,7 @@
         <v>15</v>
       </c>
       <c r="AK167" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="168" spans="1:38">
@@ -15905,7 +15908,7 @@
         <v>6</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G168" s="5" t="s">
         <v>15</v>
@@ -15983,18 +15986,18 @@
         <v>15</v>
       </c>
       <c r="AJ168" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK168" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL168" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="170" spans="1:38">
       <c r="A170" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B170" s="1">
         <v>16</v>
@@ -16084,10 +16087,10 @@
         <v>15</v>
       </c>
       <c r="AK170" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AL170" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="171" spans="1:38">
@@ -16119,7 +16122,7 @@
         <v>15</v>
       </c>
       <c r="M171" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N171" s="5" t="s">
         <v>15</v>
@@ -16143,7 +16146,7 @@
         <v>15</v>
       </c>
       <c r="V171" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W171" s="5" t="s">
         <v>15</v>
@@ -16152,19 +16155,19 @@
         <v>15</v>
       </c>
       <c r="Z171" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA171" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB171" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD171" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE171" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF171" s="5" t="s">
         <v>15</v>
@@ -16179,7 +16182,7 @@
         <v>15</v>
       </c>
       <c r="AK171" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="172" spans="1:38">
@@ -16211,7 +16214,7 @@
         <v>15</v>
       </c>
       <c r="M172" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N172" s="5" t="s">
         <v>15</v>
@@ -16235,7 +16238,7 @@
         <v>15</v>
       </c>
       <c r="V172" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W172" s="5" t="s">
         <v>15</v>
@@ -16244,19 +16247,19 @@
         <v>15</v>
       </c>
       <c r="Z172" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA172" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB172" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD172" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AE172" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF172" s="5" t="s">
         <v>15</v>
@@ -16271,7 +16274,7 @@
         <v>15</v>
       </c>
       <c r="AK172" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="173" spans="1:38">
@@ -16336,13 +16339,13 @@
         <v>15</v>
       </c>
       <c r="Z173" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA173" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB173" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD173" s="5" t="s">
         <v>15</v>
@@ -16363,7 +16366,7 @@
         <v>15</v>
       </c>
       <c r="AK173" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="174" spans="1:38">
@@ -16395,7 +16398,7 @@
         <v>15</v>
       </c>
       <c r="M174" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N174" s="5" t="s">
         <v>15</v>
@@ -16422,19 +16425,19 @@
         <v>15</v>
       </c>
       <c r="W174" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X174" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Z174" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA174" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB174" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD174" s="5" t="s">
         <v>15</v>
@@ -16443,7 +16446,7 @@
         <v>15</v>
       </c>
       <c r="AF174" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG174" s="5" t="s">
         <v>15</v>
@@ -16455,7 +16458,7 @@
         <v>15</v>
       </c>
       <c r="AK174" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="175" spans="1:38">
@@ -16487,7 +16490,7 @@
         <v>15</v>
       </c>
       <c r="M175" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N175" s="5" t="s">
         <v>15</v>
@@ -16514,19 +16517,19 @@
         <v>15</v>
       </c>
       <c r="W175" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X175" s="5" t="s">
         <v>15</v>
       </c>
       <c r="Z175" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA175" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB175" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD175" s="5" t="s">
         <v>15</v>
@@ -16535,7 +16538,7 @@
         <v>15</v>
       </c>
       <c r="AF175" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG175" s="5" t="s">
         <v>15</v>
@@ -16547,7 +16550,7 @@
         <v>15</v>
       </c>
       <c r="AK175" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="176" spans="1:38">
@@ -16558,7 +16561,7 @@
         <v>6</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G176" s="5" t="s">
         <v>15</v>
@@ -16612,13 +16615,13 @@
         <v>15</v>
       </c>
       <c r="Z176" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA176" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB176" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD176" s="5" t="s">
         <v>15</v>
@@ -16636,13 +16639,13 @@
         <v>15</v>
       </c>
       <c r="AJ176" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK176" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL176" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -16663,240 +16666,240 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" t="s">
         <v>179</v>
-      </c>
-      <c r="B2" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B3" t="s">
         <v>181</v>
-      </c>
-      <c r="B3" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" t="s">
         <v>148</v>
-      </c>
-      <c r="B9" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10" t="s">
         <v>150</v>
-      </c>
-      <c r="B10" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" t="s">
         <v>154</v>
-      </c>
-      <c r="B13" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B14" t="s">
         <v>156</v>
-      </c>
-      <c r="B14" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
+        <v>157</v>
+      </c>
+      <c r="B15" t="s">
         <v>158</v>
-      </c>
-      <c r="B15" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" t="s">
         <v>160</v>
-      </c>
-      <c r="B16" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17" t="s">
         <v>162</v>
-      </c>
-      <c r="B17" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B18" t="s">
         <v>164</v>
-      </c>
-      <c r="B18" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
+        <v>166</v>
+      </c>
+      <c r="B21" t="s">
         <v>167</v>
-      </c>
-      <c r="B21" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B22" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
+        <v>169</v>
+      </c>
+      <c r="B23" t="s">
         <v>170</v>
-      </c>
-      <c r="B23" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
+        <v>183</v>
+      </c>
+      <c r="B24" t="s">
         <v>184</v>
-      </c>
-      <c r="B24" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
+        <v>185</v>
+      </c>
+      <c r="B25" t="s">
         <v>186</v>
-      </c>
-      <c r="B25" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B27" t="s">
         <v>172</v>
-      </c>
-      <c r="B27" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B31" t="s">
         <v>176</v>
-      </c>
-      <c r="B31" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B35" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -16904,7 +16907,7 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -16912,15 +16915,15 @@
         <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B43" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -16928,23 +16931,23 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -16952,7 +16955,7 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -16960,7 +16963,7 @@
         <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -16968,15 +16971,15 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B51" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -16984,7 +16987,7 @@
         <v>4</v>
       </c>
       <c r="B52" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -16992,7 +16995,7 @@
         <v>5</v>
       </c>
       <c r="B53" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -17000,7 +17003,7 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -17008,7 +17011,7 @@
         <v>10</v>
       </c>
       <c r="B56" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -17016,60 +17019,60 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="B59" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B60" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B61" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B62" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B63" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B66" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -17080,7 +17083,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="1" max="1" width="9.3046875" style="17" customWidth="1"/>
@@ -17089,10 +17092,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -17100,27 +17103,35 @@
         <v>46205</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="B3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>227</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="16">
+        <v>46205</v>
+      </c>
+      <c r="B7" t="s">
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/CPU Design/L1IsSequences.xlsx
+++ b/CPU Design/L1IsSequences.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="103" windowWidth="14803" windowHeight="8014"/>
+    <workbookView xWindow="240" yWindow="103" windowWidth="14803" windowHeight="8014" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sequences" sheetId="4" r:id="rId1"/>
@@ -579,7 +579,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4648" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4649" uniqueCount="234">
   <si>
     <t>STEP</t>
   </si>
@@ -1303,6 +1303,9 @@
   </si>
   <si>
     <t>Most of the signals are "active low", a few are "active high"</t>
+  </si>
+  <si>
+    <t>Changed all selects and SEQ_END from active high to active low.</t>
   </si>
 </sst>
 </file>
@@ -17105,7 +17108,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="1" max="1" width="9.3046875" style="17" customWidth="1"/>
@@ -17156,6 +17159,14 @@
         <v>229</v>
       </c>
     </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="16">
+        <v>46207</v>
+      </c>
+      <c r="B8" t="s">
+        <v>233</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
